--- a/assets/layout.xlsx
+++ b/assets/layout.xlsx
@@ -5,29 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HONEY\codeDir\GeoWel\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HONEY\codeDir\reflex_proj\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1194D957-2D4C-4938-BCD1-7DCD0A22AEDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{459D3CC9-CEA4-4E33-B7EA-4369F744E8AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -560,7 +551,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -613,6 +604,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="3" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -973,29 +967,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="29" t="s">
+      <c r="C1" s="28"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="34" t="s">
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="35"/>
-      <c r="L1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="37"/>
     </row>
     <row r="2" spans="1:12" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="33"/>
+      <c r="A2" s="34"/>
       <c r="B2" s="10" t="s">
         <v>18</v>
       </c>
@@ -1005,7 +999,7 @@
       <c r="D2" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="20" t="s">
         <v>21</v>
       </c>
       <c r="F2" s="13" t="s">
@@ -1017,10 +1011,10 @@
       <c r="H2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="I2" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="19" t="s">
         <v>27</v>
       </c>
       <c r="K2" s="14" t="s">
@@ -1031,52 +1025,41 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="22">
-        <f>SUM(B4:B20)</f>
-        <v>7005</v>
-      </c>
-      <c r="C3" s="23">
-        <f>SUM(C4:C20)</f>
-        <v>1028</v>
-      </c>
-      <c r="D3" s="24">
-        <f>SUM(D4:D20)</f>
-        <v>1918</v>
-      </c>
-      <c r="E3" s="22">
-        <f>SUM(E4:E20)</f>
-        <v>7005</v>
-      </c>
-      <c r="F3" s="23">
-        <f>SUM(F4:F20)</f>
-        <v>1028</v>
-      </c>
-      <c r="G3" s="23">
-        <f>SUM(G4:G20)</f>
-        <v>1918</v>
-      </c>
-      <c r="H3" s="23">
-        <f>SUM(H4:H20)</f>
-        <v>7005</v>
-      </c>
-      <c r="I3" s="24">
-        <f>SUM(I4:I20)</f>
-        <v>1028</v>
-      </c>
-      <c r="J3" s="25">
-        <f>SUM(J4:J20)</f>
-        <v>1918</v>
-      </c>
-      <c r="K3" s="23">
-        <f>SUM(K4:K20)</f>
-        <v>7005</v>
-      </c>
-      <c r="L3" s="24">
-        <f>SUM(L4:L20)</f>
-        <v>1028</v>
+      <c r="B3" s="23">
+        <v>11565</v>
+      </c>
+      <c r="C3" s="24">
+        <v>6449</v>
+      </c>
+      <c r="D3" s="25">
+        <v>5336</v>
+      </c>
+      <c r="E3" s="23">
+        <v>14474</v>
+      </c>
+      <c r="F3" s="24">
+        <v>40537</v>
+      </c>
+      <c r="G3" s="24">
+        <v>7649</v>
+      </c>
+      <c r="H3" s="24">
+        <v>1334</v>
+      </c>
+      <c r="I3" s="25">
+        <v>2098</v>
+      </c>
+      <c r="J3" s="26">
+        <v>1307</v>
+      </c>
+      <c r="K3" s="24">
+        <v>23.2</v>
+      </c>
+      <c r="L3" s="25">
+        <v>623</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
@@ -1084,37 +1067,37 @@
         <v>1</v>
       </c>
       <c r="B4" s="5">
-        <v>1234</v>
+        <v>1176</v>
       </c>
       <c r="C4" s="3">
-        <v>123</v>
+        <v>698</v>
       </c>
       <c r="D4" s="6">
-        <v>1234</v>
+        <v>642</v>
       </c>
       <c r="E4" s="5">
-        <v>1234</v>
+        <v>3376</v>
       </c>
       <c r="F4" s="3">
-        <v>123</v>
+        <v>5695</v>
       </c>
       <c r="G4" s="3">
-        <v>1234</v>
+        <v>1518</v>
       </c>
       <c r="H4" s="3">
-        <v>1234</v>
+        <v>238</v>
       </c>
       <c r="I4" s="6">
-        <v>123</v>
+        <v>313</v>
       </c>
       <c r="J4" s="4">
-        <v>1234</v>
+        <v>103</v>
       </c>
       <c r="K4" s="3">
-        <v>1234</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="L4" s="6">
-        <v>123</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
@@ -1122,37 +1105,37 @@
         <v>2</v>
       </c>
       <c r="B5" s="5">
-        <v>123</v>
+        <v>274</v>
       </c>
       <c r="C5" s="3">
-        <v>123</v>
+        <v>172</v>
       </c>
       <c r="D5" s="6">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="E5" s="5">
-        <v>123</v>
+        <v>891</v>
       </c>
       <c r="F5" s="3">
-        <v>123</v>
+        <v>2467</v>
       </c>
       <c r="G5" s="3">
-        <v>123</v>
+        <v>364</v>
       </c>
       <c r="H5" s="3">
-        <v>123</v>
+        <v>54</v>
       </c>
       <c r="I5" s="6">
-        <v>123</v>
+        <v>173</v>
       </c>
       <c r="J5" s="4">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="K5" s="3">
-        <v>123</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="L5" s="6">
-        <v>123</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
@@ -1160,37 +1143,37 @@
         <v>3</v>
       </c>
       <c r="B6" s="5">
-        <v>1234</v>
+        <v>146</v>
       </c>
       <c r="C6" s="3">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="D6" s="6">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="E6" s="5">
-        <v>1234</v>
+        <v>614</v>
       </c>
       <c r="F6" s="3">
-        <v>12</v>
+        <v>2148</v>
       </c>
       <c r="G6" s="3">
-        <v>13</v>
+        <v>381</v>
       </c>
       <c r="H6" s="3">
-        <v>1234</v>
+        <v>59</v>
       </c>
       <c r="I6" s="6">
-        <v>12</v>
+        <v>102</v>
       </c>
       <c r="J6" s="4">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="K6" s="3">
-        <v>1234</v>
+        <v>14.8</v>
       </c>
       <c r="L6" s="6">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
@@ -1198,37 +1181,37 @@
         <v>4</v>
       </c>
       <c r="B7" s="5">
-        <v>1234</v>
+        <v>237</v>
       </c>
       <c r="C7" s="3">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="D7" s="6">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="E7" s="5">
-        <v>1234</v>
+        <v>700</v>
       </c>
       <c r="F7" s="3">
-        <v>123</v>
+        <v>2558</v>
       </c>
       <c r="G7" s="3">
-        <v>23</v>
+        <v>347</v>
       </c>
       <c r="H7" s="3">
-        <v>1234</v>
+        <v>53</v>
       </c>
       <c r="I7" s="6">
-        <v>123</v>
+        <v>69</v>
       </c>
       <c r="J7" s="4">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="K7" s="3">
-        <v>1234</v>
+        <v>17.3</v>
       </c>
       <c r="L7" s="6">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
@@ -1236,37 +1219,37 @@
         <v>5</v>
       </c>
       <c r="B8" s="5">
-        <v>123</v>
+        <v>1425</v>
       </c>
       <c r="C8" s="3">
-        <v>12</v>
+        <v>450</v>
       </c>
       <c r="D8" s="6">
+        <v>379</v>
+      </c>
+      <c r="E8" s="5">
+        <v>495</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1436</v>
+      </c>
+      <c r="G8" s="3">
+        <v>162</v>
+      </c>
+      <c r="H8" s="3">
+        <v>37</v>
+      </c>
+      <c r="I8" s="6">
+        <v>45</v>
+      </c>
+      <c r="J8" s="4">
+        <v>60</v>
+      </c>
+      <c r="K8" s="3">
+        <v>17.8</v>
+      </c>
+      <c r="L8" s="6">
         <v>13</v>
-      </c>
-      <c r="E8" s="5">
-        <v>123</v>
-      </c>
-      <c r="F8" s="3">
-        <v>12</v>
-      </c>
-      <c r="G8" s="3">
-        <v>13</v>
-      </c>
-      <c r="H8" s="3">
-        <v>123</v>
-      </c>
-      <c r="I8" s="6">
-        <v>12</v>
-      </c>
-      <c r="J8" s="4">
-        <v>13</v>
-      </c>
-      <c r="K8" s="3">
-        <v>123</v>
-      </c>
-      <c r="L8" s="6">
-        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
@@ -1274,37 +1257,37 @@
         <v>6</v>
       </c>
       <c r="B9" s="5">
-        <v>123</v>
+        <v>752</v>
       </c>
       <c r="C9" s="3">
-        <v>13</v>
+        <v>487</v>
       </c>
       <c r="D9" s="6">
+        <v>294</v>
+      </c>
+      <c r="E9" s="5">
+        <v>504</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1390</v>
+      </c>
+      <c r="G9" s="3">
+        <v>153</v>
+      </c>
+      <c r="H9" s="3">
         <v>23</v>
       </c>
-      <c r="E9" s="5">
-        <v>123</v>
-      </c>
-      <c r="F9" s="3">
-        <v>13</v>
-      </c>
-      <c r="G9" s="3">
-        <v>23</v>
-      </c>
-      <c r="H9" s="3">
-        <v>123</v>
-      </c>
       <c r="I9" s="6">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="J9" s="4">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="K9" s="3">
-        <v>123</v>
+        <v>11.6</v>
       </c>
       <c r="L9" s="6">
-        <v>13</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.45">
@@ -1312,37 +1295,37 @@
         <v>7</v>
       </c>
       <c r="B10" s="5">
-        <v>123</v>
+        <v>41</v>
       </c>
       <c r="C10" s="3">
-        <v>123</v>
+        <v>26</v>
       </c>
       <c r="D10" s="6">
         <v>23</v>
       </c>
       <c r="E10" s="5">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="F10" s="3">
-        <v>123</v>
+        <v>780</v>
       </c>
       <c r="G10" s="3">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="H10" s="3">
-        <v>123</v>
+        <v>21</v>
       </c>
       <c r="I10" s="6">
-        <v>123</v>
+        <v>30</v>
       </c>
       <c r="J10" s="4">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="K10" s="3">
-        <v>123</v>
+        <v>14.8</v>
       </c>
       <c r="L10" s="6">
-        <v>123</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.45">
@@ -1350,37 +1333,37 @@
         <v>8</v>
       </c>
       <c r="B11" s="5">
-        <v>13</v>
+        <v>1797</v>
       </c>
       <c r="C11" s="3">
-        <v>23</v>
+        <v>1278</v>
       </c>
       <c r="D11" s="6">
-        <v>123</v>
+        <v>1095</v>
       </c>
       <c r="E11" s="5">
-        <v>13</v>
+        <v>3087</v>
       </c>
       <c r="F11" s="3">
-        <v>23</v>
+        <v>8854</v>
       </c>
       <c r="G11" s="3">
-        <v>123</v>
+        <v>1642</v>
       </c>
       <c r="H11" s="3">
-        <v>13</v>
+        <v>240</v>
       </c>
       <c r="I11" s="6">
-        <v>23</v>
+        <v>346</v>
       </c>
       <c r="J11" s="4">
-        <v>123</v>
+        <v>275</v>
       </c>
       <c r="K11" s="3">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="L11" s="6">
-        <v>23</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.45">
@@ -1388,37 +1371,37 @@
         <v>9</v>
       </c>
       <c r="B12" s="5">
-        <v>23</v>
+        <v>808</v>
       </c>
       <c r="C12" s="3">
-        <v>12</v>
+        <v>479</v>
       </c>
       <c r="D12" s="6">
-        <v>123</v>
+        <v>333</v>
       </c>
       <c r="E12" s="5">
-        <v>23</v>
+        <v>452</v>
       </c>
       <c r="F12" s="3">
-        <v>12</v>
+        <v>1219</v>
       </c>
       <c r="G12" s="3">
-        <v>123</v>
+        <v>331</v>
       </c>
       <c r="H12" s="3">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="I12" s="6">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="J12" s="4">
-        <v>123</v>
+        <v>35</v>
       </c>
       <c r="K12" s="3">
-        <v>23</v>
+        <v>26.9</v>
       </c>
       <c r="L12" s="6">
-        <v>12</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.45">
@@ -1426,37 +1409,37 @@
         <v>10</v>
       </c>
       <c r="B13" s="5">
-        <v>123</v>
+        <v>780</v>
       </c>
       <c r="C13" s="3">
-        <v>23</v>
+        <v>439</v>
       </c>
       <c r="D13" s="6">
-        <v>13</v>
+        <v>112</v>
       </c>
       <c r="E13" s="5">
-        <v>123</v>
+        <v>614</v>
       </c>
       <c r="F13" s="3">
-        <v>23</v>
+        <v>2076</v>
       </c>
       <c r="G13" s="3">
-        <v>13</v>
+        <v>310</v>
       </c>
       <c r="H13" s="3">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="I13" s="6">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="J13" s="4">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="K13" s="3">
-        <v>123</v>
+        <v>27.4</v>
       </c>
       <c r="L13" s="6">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.45">
@@ -1464,37 +1447,37 @@
         <v>11</v>
       </c>
       <c r="B14" s="5">
-        <v>1234</v>
+        <v>1016</v>
       </c>
       <c r="C14" s="3">
-        <v>13</v>
+        <v>572</v>
       </c>
       <c r="D14" s="6">
-        <v>12</v>
+        <v>648</v>
       </c>
       <c r="E14" s="5">
-        <v>1234</v>
+        <v>705</v>
       </c>
       <c r="F14" s="3">
-        <v>13</v>
+        <v>2080</v>
       </c>
       <c r="G14" s="3">
-        <v>12</v>
+        <v>437</v>
       </c>
       <c r="H14" s="3">
-        <v>1234</v>
+        <v>127</v>
       </c>
       <c r="I14" s="6">
-        <v>13</v>
+        <v>195</v>
       </c>
       <c r="J14" s="4">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="K14" s="3">
-        <v>1234</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="L14" s="6">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.45">
@@ -1502,37 +1485,37 @@
         <v>12</v>
       </c>
       <c r="B15" s="5">
-        <v>12</v>
+        <v>1024</v>
       </c>
       <c r="C15" s="3">
-        <v>123</v>
+        <v>454</v>
       </c>
       <c r="D15" s="6">
-        <v>13</v>
+        <v>363</v>
       </c>
       <c r="E15" s="5">
-        <v>12</v>
+        <v>551</v>
       </c>
       <c r="F15" s="3">
-        <v>123</v>
+        <v>2662</v>
       </c>
       <c r="G15" s="3">
-        <v>13</v>
+        <v>421</v>
       </c>
       <c r="H15" s="3">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="I15" s="6">
-        <v>123</v>
+        <v>200</v>
       </c>
       <c r="J15" s="4">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="K15" s="3">
-        <v>12</v>
+        <v>22.9</v>
       </c>
       <c r="L15" s="6">
-        <v>123</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.45">
@@ -1540,37 +1523,37 @@
         <v>13</v>
       </c>
       <c r="B16" s="5">
-        <v>13</v>
+        <v>606</v>
       </c>
       <c r="C16" s="3">
-        <v>123</v>
+        <v>451</v>
       </c>
       <c r="D16" s="6">
-        <v>23</v>
+        <v>294</v>
       </c>
       <c r="E16" s="5">
-        <v>13</v>
+        <v>720</v>
       </c>
       <c r="F16" s="3">
-        <v>123</v>
+        <v>3257</v>
       </c>
       <c r="G16" s="3">
-        <v>23</v>
+        <v>431</v>
       </c>
       <c r="H16" s="3">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="I16" s="6">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="J16" s="4">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="K16" s="3">
-        <v>13</v>
+        <v>18.2</v>
       </c>
       <c r="L16" s="6">
-        <v>123</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.45">
@@ -1578,37 +1561,37 @@
         <v>14</v>
       </c>
       <c r="B17" s="5">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="C17" s="3">
-        <v>123</v>
+        <v>45</v>
       </c>
       <c r="D17" s="6">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="E17" s="5">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="F17" s="3">
-        <v>123</v>
+        <v>375</v>
       </c>
       <c r="G17" s="3">
-        <v>12</v>
+        <v>151</v>
       </c>
       <c r="H17" s="3">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I17" s="6">
-        <v>123</v>
+        <v>10</v>
       </c>
       <c r="J17" s="4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K17" s="3">
-        <v>23</v>
+        <v>13.9</v>
       </c>
       <c r="L17" s="6">
-        <v>123</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.45">
@@ -1616,37 +1599,37 @@
         <v>15</v>
       </c>
       <c r="B18" s="5">
-        <v>123</v>
+        <v>38</v>
       </c>
       <c r="C18" s="3">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D18" s="6">
-        <v>12</v>
-      </c>
-      <c r="E18" s="6">
-        <v>123</v>
-      </c>
-      <c r="F18" s="6">
-        <v>23</v>
-      </c>
-      <c r="G18" s="6">
-        <v>12</v>
-      </c>
-      <c r="H18" s="6">
-        <v>123</v>
+        <v>3</v>
+      </c>
+      <c r="E18" s="5">
+        <v>71</v>
+      </c>
+      <c r="F18" s="3">
+        <v>130</v>
+      </c>
+      <c r="G18" s="3">
+        <v>20</v>
+      </c>
+      <c r="H18" s="3">
+        <v>4</v>
       </c>
       <c r="I18" s="6">
-        <v>23</v>
-      </c>
-      <c r="J18" s="6">
-        <v>12</v>
-      </c>
-      <c r="K18" s="6">
-        <v>123</v>
+        <v>8</v>
+      </c>
+      <c r="J18" s="4">
+        <v>3</v>
+      </c>
+      <c r="K18" s="3">
+        <v>72.5</v>
       </c>
       <c r="L18" s="6">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.45">
@@ -1654,37 +1637,37 @@
         <v>16</v>
       </c>
       <c r="B19" s="5">
-        <v>1234</v>
+        <v>771</v>
       </c>
       <c r="C19" s="3">
-        <v>13</v>
+        <v>405</v>
       </c>
       <c r="D19" s="6">
-        <v>12</v>
-      </c>
-      <c r="E19" s="6">
-        <v>1234</v>
-      </c>
-      <c r="F19" s="6">
-        <v>13</v>
-      </c>
-      <c r="G19" s="6">
-        <v>12</v>
-      </c>
-      <c r="H19" s="6">
-        <v>1234</v>
+        <v>521</v>
+      </c>
+      <c r="E19" s="5">
+        <v>714</v>
+      </c>
+      <c r="F19" s="3">
+        <v>2243</v>
+      </c>
+      <c r="G19" s="3">
+        <v>376</v>
+      </c>
+      <c r="H19" s="3">
+        <v>91</v>
       </c>
       <c r="I19" s="6">
-        <v>13</v>
-      </c>
-      <c r="J19" s="6">
-        <v>12</v>
-      </c>
-      <c r="K19" s="6">
-        <v>1234</v>
+        <v>153</v>
+      </c>
+      <c r="J19" s="4">
+        <v>73</v>
+      </c>
+      <c r="K19" s="3">
+        <v>12.8</v>
       </c>
       <c r="L19" s="6">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -1692,37 +1675,37 @@
         <v>17</v>
       </c>
       <c r="B20" s="7">
-        <v>13</v>
+        <v>585</v>
       </c>
       <c r="C20" s="8">
-        <v>23</v>
+        <v>297</v>
       </c>
       <c r="D20" s="9">
-        <v>123</v>
-      </c>
-      <c r="E20" s="9">
-        <v>13</v>
-      </c>
-      <c r="F20" s="9">
-        <v>23</v>
-      </c>
-      <c r="G20" s="9">
-        <v>123</v>
-      </c>
-      <c r="H20" s="9">
-        <v>13</v>
+        <v>282</v>
+      </c>
+      <c r="E20" s="7">
+        <v>680</v>
+      </c>
+      <c r="F20" s="8">
+        <v>1167</v>
+      </c>
+      <c r="G20" s="8">
+        <v>530</v>
+      </c>
+      <c r="H20" s="8">
+        <v>102</v>
       </c>
       <c r="I20" s="9">
-        <v>23</v>
-      </c>
-      <c r="J20" s="9">
-        <v>123</v>
-      </c>
-      <c r="K20" s="9">
-        <v>13</v>
+        <v>122</v>
+      </c>
+      <c r="J20" s="18">
+        <v>32</v>
+      </c>
+      <c r="K20" s="8">
+        <v>32.4</v>
       </c>
       <c r="L20" s="9">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.45">
